--- a/Speciallægeloft/speciallægeloft_data/Sjælland+Steno_Sjælland.xlsx
+++ b/Speciallægeloft/speciallægeloft_data/Sjælland+Steno_Sjælland.xlsx
@@ -40,7 +40,7 @@
     <t>Datasæt 12 2025</t>
   </si>
   <si>
-    <t>Kørsel 15.4.2026 14.33.27</t>
+    <t>Kørsel 15.4.2026 14.35.15</t>
   </si>
   <si>
     <t/>
